--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8182-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8182-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0647BFFC-95E6-43D6-8E60-121ADA68FCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FFD28D5-C17C-48FF-8264-C463E0BB9B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{327BF727-E6D8-4A2C-B0EE-4AF7E018359B}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{AFFD6437-AEB5-4127-A580-C2BF3C1C53CB}"/>
   </bookViews>
   <sheets>
     <sheet name="8182-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1508,30 +1508,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942E209B-0115-456B-9E2F-76F7CC6C0C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37FF4D88-39A3-4E9F-92F7-E7A605B831F9}">
   <dimension ref="A1:X35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1565,7 +1565,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1601,7 +1601,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1721,7 +1721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>8.18</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>32</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>32</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>32</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2020</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>32</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>32</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2019</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2018</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2017</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>7.43</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2016</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2015</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2014</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2013</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2012</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2011</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2010</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2009</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2008</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2007</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2006</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2005</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2004</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>9.44</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2003</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2001</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2000</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1999</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38" t="s">
         <v>56</v>
       </c>
